--- a/backend/data/financials_by_company/18H0.F.xlsx
+++ b/backend/data/financials_by_company/18H0.F.xlsx
@@ -4117,7 +4117,7 @@
         <v>-3118112</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>0.0014599999</v>
